--- a/Roles_Sprints (2).xlsx
+++ b/Roles_Sprints (2).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/D33EB122056A01AA/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a49a8ce05e8191ac/Desktop/DevOps/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E7160DD-597A-4779-A701-C67237E0D723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{4E7160DD-597A-4779-A701-C67237E0D723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4807CB2D-499E-4A80-AB8E-095029D55EDE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="226">
   <si>
     <t>Name</t>
   </si>
@@ -152,9 +152,6 @@
   </si>
   <si>
     <t>Design HR Management Page</t>
-  </si>
-  <si>
-    <t>Design Employee Management Page</t>
   </si>
   <si>
     <t>Design Asset Management Page</t>
@@ -742,7 +739,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1157,16 +1154,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F197"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.85546875" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.88671875" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1184,7 +1181,7 @@
       </c>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1201,27 +1198,27 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
         <v>14</v>
       </c>
@@ -1229,22 +1226,22 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
         <v>18</v>
       </c>
@@ -1252,17 +1249,17 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E14" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E15" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="4:5">
+    <row r="17" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
         <v>22</v>
       </c>
@@ -1270,17 +1267,17 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="4:5">
+    <row r="18" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E18" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="4:5">
+    <row r="19" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E19" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="4:5">
+    <row r="21" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
         <v>24</v>
       </c>
@@ -1288,17 +1285,17 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="4:5">
+    <row r="22" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E22" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="4:5">
+    <row r="23" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E23" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="4:5">
+    <row r="25" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D25" t="s">
         <v>26</v>
       </c>
@@ -1306,17 +1303,17 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="4:5">
+    <row r="26" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E26" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="4:5">
+    <row r="27" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E27" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="4:5">
+    <row r="29" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
         <v>28</v>
       </c>
@@ -1324,17 +1321,17 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="4:5">
+    <row r="30" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E30" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="4:5">
+    <row r="31" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E31" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -1351,17 +1348,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E34" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E35" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D37" t="s">
         <v>14</v>
       </c>
@@ -1369,757 +1366,752 @@
         <v>38</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E38" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E39" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
-      <c r="E40" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D42" t="s">
         <v>18</v>
       </c>
       <c r="E42" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E43" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
-      <c r="E43" t="s">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E44" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
-      <c r="E44" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D46" t="s">
         <v>22</v>
       </c>
       <c r="E46" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E47" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
-      <c r="E47" t="s">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E48" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
-      <c r="E48" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D50" t="s">
         <v>24</v>
       </c>
       <c r="E50" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E51" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
-      <c r="E51" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
         <v>26</v>
       </c>
       <c r="E53" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E54" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
-      <c r="E54" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D56" t="s">
         <v>28</v>
       </c>
       <c r="E56" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E57" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
-      <c r="E57" t="s">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" t="s">
+      <c r="B59" t="s">
         <v>54</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
         <v>55</v>
-      </c>
-      <c r="C59" t="s">
-        <v>56</v>
       </c>
       <c r="D59" t="s">
         <v>8</v>
       </c>
       <c r="E59" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E60" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
-      <c r="E60" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D62" t="s">
         <v>14</v>
       </c>
       <c r="E62" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E63" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
-      <c r="E63" t="s">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E64" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
-      <c r="E64" t="s">
+    <row r="65" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E65" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="4:5">
-      <c r="E65" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="67" spans="4:5">
+    <row r="67" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D67" t="s">
         <v>18</v>
       </c>
       <c r="E67" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="68" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E68" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="68" spans="4:5">
-      <c r="E68" t="s">
+    <row r="69" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E69" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="69" spans="4:5">
-      <c r="E69" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="71" spans="4:5">
+    <row r="71" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D71" t="s">
         <v>22</v>
       </c>
       <c r="E71" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="72" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E72" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="72" spans="4:5">
-      <c r="E72" t="s">
+    <row r="73" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E73" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="73" spans="4:5">
-      <c r="E73" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="75" spans="4:5">
+    <row r="75" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D75" t="s">
         <v>24</v>
       </c>
       <c r="E75" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="76" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E76" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="76" spans="4:5">
-      <c r="E76" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="78" spans="4:5">
+    <row r="78" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D78" t="s">
         <v>26</v>
       </c>
       <c r="E78" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="79" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E79" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="79" spans="4:5">
-      <c r="E79" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D81" t="s">
         <v>28</v>
       </c>
       <c r="E81" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E82" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
-      <c r="E82" t="s">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" t="s">
+      <c r="B84" t="s">
         <v>75</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" t="s">
         <v>76</v>
-      </c>
-      <c r="C84" t="s">
-        <v>77</v>
       </c>
       <c r="D84" t="s">
         <v>8</v>
       </c>
       <c r="E84" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E85" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
-      <c r="E85" t="s">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E86" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
-      <c r="E86" t="s">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E87" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
-      <c r="E87" t="s">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E88" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
-      <c r="E88" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D90" t="s">
         <v>14</v>
       </c>
       <c r="E90" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E91" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
-      <c r="E91" t="s">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E92" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
-      <c r="E92" t="s">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E93" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
-      <c r="E93" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D95" t="s">
         <v>18</v>
       </c>
       <c r="E95" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E96" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
-      <c r="E96" t="s">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E97" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
-      <c r="E97" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D99" t="s">
         <v>22</v>
       </c>
       <c r="E99" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E100" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
-      <c r="E100" t="s">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E101" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="101" spans="1:5">
-      <c r="E101" t="s">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D103" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="103" spans="1:5">
-      <c r="D103" t="s">
+      <c r="E103" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E103" s="6" t="s">
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E104" s="6" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
-      <c r="E104" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D106" t="s">
         <v>26</v>
       </c>
       <c r="E106" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E107" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="107" spans="1:5">
-      <c r="E107" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D109" t="s">
         <v>28</v>
       </c>
       <c r="E109" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E110" s="6" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
-      <c r="E110" s="6" t="s">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="112" spans="1:5">
-      <c r="A112" t="s">
+      <c r="B112" t="s">
         <v>100</v>
       </c>
-      <c r="B112" t="s">
+      <c r="C112" t="s">
         <v>101</v>
-      </c>
-      <c r="C112" t="s">
-        <v>102</v>
       </c>
       <c r="D112" t="s">
         <v>8</v>
       </c>
       <c r="E112" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="113" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E113" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="113" spans="4:5">
-      <c r="E113" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="115" spans="4:5">
+    <row r="115" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D115" t="s">
         <v>14</v>
       </c>
       <c r="E115" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="116" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E116" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="116" spans="4:5">
-      <c r="E116" t="s">
+    <row r="117" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E117" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="117" spans="4:5">
-      <c r="E117" t="s">
+    <row r="118" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E118" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="118" spans="4:5">
-      <c r="E118" t="s">
+    <row r="119" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E119" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="119" spans="4:5">
-      <c r="E119" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="121" spans="4:5">
+    <row r="121" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D121" t="s">
         <v>18</v>
       </c>
       <c r="E121" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="122" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E122" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="122" spans="4:5">
-      <c r="E122" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="123" spans="4:5">
+    <row r="123" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E123" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="124" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E124" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="124" spans="4:5">
-      <c r="E124" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="126" spans="4:5">
+    <row r="126" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D126" t="s">
         <v>22</v>
       </c>
       <c r="E126" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="127" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E127" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="127" spans="4:5">
-      <c r="E127" t="s">
+    <row r="128" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E128" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="128" spans="4:5">
-      <c r="E128" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="129" spans="4:5">
+    <row r="129" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E129" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="130" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E130" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="130" spans="4:5">
-      <c r="E130" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="132" spans="4:5">
+    <row r="132" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D132" t="s">
         <v>24</v>
       </c>
       <c r="E132" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="133" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E133" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="133" spans="4:5">
-      <c r="E133" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="134" spans="4:5">
+    <row r="134" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E134" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="135" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E135" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="135" spans="4:5">
-      <c r="E135" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="137" spans="4:5">
+    <row r="137" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D137" t="s">
         <v>26</v>
       </c>
       <c r="E137" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="138" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E138" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="138" spans="4:5">
-      <c r="E138" t="s">
+    <row r="139" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E139" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="139" spans="4:5">
-      <c r="E139" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="141" spans="4:5">
+    <row r="141" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D141" t="s">
         <v>28</v>
       </c>
       <c r="E141" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="142" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E142" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="142" spans="4:5">
-      <c r="E142" t="s">
+    <row r="143" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E143" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="143" spans="4:5">
-      <c r="E143" t="s">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="145" spans="1:5">
-      <c r="A145" t="s">
+      <c r="B145" t="s">
         <v>123</v>
       </c>
-      <c r="B145" t="s">
+      <c r="C145" t="s">
         <v>124</v>
-      </c>
-      <c r="C145" t="s">
-        <v>125</v>
       </c>
       <c r="D145" t="s">
         <v>8</v>
       </c>
       <c r="E145" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E146" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="146" spans="1:5">
-      <c r="E146" t="s">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E147" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="147" spans="1:5">
-      <c r="E147" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D149" t="s">
         <v>14</v>
       </c>
       <c r="E149" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E150" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="150" spans="1:5">
-      <c r="E150" t="s">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E151" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
-      <c r="E151" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D153" t="s">
         <v>18</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E154" s="6" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E155" s="6"/>
     </row>
-    <row r="157" spans="1:5">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D157" t="s">
         <v>22</v>
       </c>
       <c r="E157" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E158" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D161" t="s">
         <v>24</v>
       </c>
       <c r="E161" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E162" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D164" t="s">
         <v>26</v>
       </c>
       <c r="E164" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E165" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="165" spans="1:5">
-      <c r="E165" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D168" t="s">
         <v>28</v>
       </c>
       <c r="E168" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E169" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="169" spans="1:5">
-      <c r="E169" t="s">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E170" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="170" spans="1:5">
-      <c r="E170" t="s">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="172" spans="1:5">
-      <c r="A172" t="s">
+      <c r="B172" t="s">
         <v>139</v>
       </c>
-      <c r="B172" t="s">
+      <c r="C172" t="s">
         <v>140</v>
-      </c>
-      <c r="C172" t="s">
-        <v>141</v>
       </c>
       <c r="D172" t="s">
         <v>8</v>
       </c>
       <c r="E172" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E173" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="173" spans="1:5">
-      <c r="E173" t="s">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E174" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="174" spans="1:5">
-      <c r="E174" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D176" t="s">
         <v>14</v>
       </c>
       <c r="E176" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="177" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E177" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="177" spans="4:5">
-      <c r="E177" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="179" spans="4:5">
+    <row r="179" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D179" t="s">
         <v>18</v>
       </c>
       <c r="E179" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="180" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E180" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="180" spans="4:5">
-      <c r="E180" t="s">
+    <row r="181" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E181" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="181" spans="4:5">
-      <c r="E181" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="183" spans="4:5">
+    <row r="183" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D183" t="s">
         <v>22</v>
       </c>
       <c r="E183" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="184" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E184" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="184" spans="4:5">
-      <c r="E184" t="s">
+    <row r="185" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E185" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="185" spans="4:5">
-      <c r="E185" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="187" spans="4:5">
+    <row r="187" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D187" t="s">
         <v>24</v>
       </c>
       <c r="E187" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="188" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E188" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="188" spans="4:5">
-      <c r="E188" t="s">
+    <row r="189" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E189" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="189" spans="4:5">
-      <c r="E189" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="191" spans="4:5">
+    <row r="191" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D191" t="s">
         <v>26</v>
       </c>
       <c r="E191" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="192" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E192" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="192" spans="4:5">
-      <c r="E192" t="s">
+    <row r="193" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E193" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="193" spans="4:5">
-      <c r="E193" t="s">
+    <row r="194" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E194" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="194" spans="4:5">
-      <c r="E194" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="196" spans="4:5">
+    <row r="196" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D196" t="s">
         <v>28</v>
       </c>
       <c r="E196" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="197" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E197" t="s">
         <v>160</v>
-      </c>
-    </row>
-    <row r="197" spans="4:5">
-      <c r="E197" t="s">
-        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -2132,351 +2124,351 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9243151F-63A6-447D-BD01-C342AF245B0F}">
   <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="33.5703125" customWidth="1"/>
+    <col min="3" max="3" width="33.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="21">
+    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.6">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.6">
+    <row r="3" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
         <v>165</v>
       </c>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4" spans="1:4" ht="15.6">
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>166</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B5" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" ht="15.6">
-      <c r="B5" s="5" t="s">
+      <c r="C5" t="s">
         <v>168</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
         <v>169</v>
       </c>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:4" ht="15.6">
-      <c r="B6" t="s">
+      <c r="C6" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
         <v>171</v>
       </c>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" ht="15.6">
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>172</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
         <v>173</v>
       </c>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:4" ht="15.6">
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>174</v>
       </c>
-      <c r="C8" t="s">
-        <v>175</v>
-      </c>
       <c r="D8" s="2"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
       <c r="B10" t="s">
+        <v>175</v>
+      </c>
+      <c r="C10" t="s">
         <v>176</v>
       </c>
-      <c r="C10" t="s">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>178</v>
       </c>
-      <c r="C11" t="s">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>180</v>
       </c>
-      <c r="C12" t="s">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>182</v>
       </c>
-      <c r="C13" t="s">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>184</v>
       </c>
-      <c r="C14" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>18</v>
       </c>
       <c r="B16" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
       <c r="B19" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
       <c r="B20" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>22</v>
       </c>
       <c r="B22" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="28.9">
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
       <c r="B23" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
       <c r="B24" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B28" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
       <c r="B30" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="5"/>
       <c r="B31" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="C31" s="5" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
       <c r="B32" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B34" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="C34" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
       <c r="B35" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
       <c r="B36" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="5"/>
       <c r="B37" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B38" s="5"/>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="5"/>
       <c r="B40" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="5"/>
       <c r="B41" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>225</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>226</v>
       </c>
     </row>
   </sheetData>
